--- a/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente</t>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 16,41</t>
+          <t>5,14; 15,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,92</t>
+          <t>1,29; 10,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,54</t>
+          <t>2,16; 12,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 11,01</t>
+          <t>1,96; 11,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 11,77</t>
+          <t>4,88; 11,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,13</t>
+          <t>2,38; 8,61</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,68</t>
+          <t>5,1; 8,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,04</t>
+          <t>4,34; 8,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,76</t>
+          <t>4,26; 7,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,09</t>
+          <t>3,62; 6,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,65</t>
+          <t>4,99; 7,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,9</t>
+          <t>4,49; 6,83</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 26,22</t>
+          <t>15,85; 26,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 23,64</t>
+          <t>13,91; 23,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,26</t>
+          <t>15,25; 25,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 20,15</t>
+          <t>12,05; 20,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 24,27</t>
+          <t>16,67; 24,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,09</t>
+          <t>14,03; 20,46</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,31</t>
+          <t>8,59; 12,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,93</t>
+          <t>7,26; 10,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,38; 10,71</t>
+          <t>7,31; 10,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 9,55</t>
+          <t>6,22; 9,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,12</t>
+          <t>8,45; 11,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 9,73</t>
+          <t>7,24; 9,55</t>
         </is>
       </c>
     </row>
@@ -920,4 +921,587 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8738</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13692</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6252</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>4705; 14605</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>764; 6167</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1844; 10401</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1348; 7726</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8633; 21180</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3047; 11024</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30289</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28133</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28417</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24606</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>58707</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52739</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>22797; 39760</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20343; 37551</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21008; 37512</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17458; 33696</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>46909; 70953</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>42716; 64969</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>34102</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31492</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>33863</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29430</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67965</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>60922</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>26263; 44063</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23950; 40310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>25940; 43227</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22525; 38935</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>55976; 80663</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>50393; 73474</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>73130</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>140364</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>119913</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>60499; 87864</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50824; 75219</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54748; 80888</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45900; 69992</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>122778; 160346</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>104068; 137380</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 15,94</t>
+          <t>5,27; 15,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,39</t>
+          <t>0,94; 11,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 12,18</t>
+          <t>2,42; 11,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,26</t>
+          <t>2,0; 12,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,97</t>
+          <t>4,65; 11,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,61</t>
+          <t>2,33; 9,03</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,9</t>
+          <t>5,02; 8,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,02</t>
+          <t>4,36; 7,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,6</t>
+          <t>4,14; 7,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,98</t>
+          <t>3,68; 7,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,55</t>
+          <t>5,07; 7,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,83</t>
+          <t>4,41; 6,92</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 26,59</t>
+          <t>15,57; 26,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 23,4</t>
+          <t>13,71; 23,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,25; 25,41</t>
+          <t>15,26; 25,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,05; 20,83</t>
+          <t>11,57; 19,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 24,02</t>
+          <t>16,84; 24,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,03; 20,46</t>
+          <t>13,84; 20,33</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 12,48</t>
+          <t>8,75; 12,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 10,75</t>
+          <t>7,2; 10,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,8</t>
+          <t>7,42; 10,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,48</t>
+          <t>6,36; 9,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,04</t>
+          <t>8,41; 10,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,55</t>
+          <t>7,27; 9,75</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4705; 14605</t>
+          <t>4832; 14317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>764; 6167</t>
+          <t>559; 6573</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1844; 10401</t>
+          <t>2071; 10067</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1348; 7726</t>
+          <t>1376; 8435</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8633; 21180</t>
+          <t>8232; 21101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3047; 11024</t>
+          <t>2981; 11561</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22797; 39760</t>
+          <t>22437; 39597</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20343; 37551</t>
+          <t>20410; 37435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21008; 37512</t>
+          <t>20439; 37101</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17458; 33696</t>
+          <t>17741; 33945</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46909; 70953</t>
+          <t>47644; 71004</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42716; 64969</t>
+          <t>41972; 65844</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26263; 44063</t>
+          <t>25805; 43757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23950; 40310</t>
+          <t>23612; 40121</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25940; 43227</t>
+          <t>25957; 43338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22525; 38935</t>
+          <t>21624; 37211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55976; 80663</t>
+          <t>56569; 80845</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>50393; 73474</t>
+          <t>49716; 73027</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60499; 87864</t>
+          <t>61583; 87539</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50824; 75219</t>
+          <t>50423; 73028</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54748; 80888</t>
+          <t>55595; 81302</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45900; 69992</t>
+          <t>46929; 69529</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122778; 160346</t>
+          <t>122203; 158271</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104068; 137380</t>
+          <t>104562; 140196</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Estudios-trans_dic.xlsx
@@ -520,13 +520,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -594,22 +594,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>9,54%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>4,5%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 15,63</t>
+          <t>2,31; 12,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,07</t>
+          <t>1,95; 11,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 11,79</t>
+          <t>4,93; 16,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,29</t>
+          <t>1,26; 10,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,92</t>
+          <t>4,73; 11,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,03</t>
+          <t>2,31; 9,13</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>6,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>6,01%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,86</t>
+          <t>4,36; 7,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,99</t>
+          <t>3,56; 7,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,52</t>
+          <t>5,04; 8,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,03</t>
+          <t>4,48; 8,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,55</t>
+          <t>5,15; 7,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,92</t>
+          <t>4,48; 6,9</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19,9%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>20,58%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>18,28%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,57; 26,4</t>
+          <t>14,99; 25,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 23,29</t>
+          <t>11,8; 20,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,26; 25,47</t>
+          <t>15,83; 26,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 19,91</t>
+          <t>14,41; 23,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 24,07</t>
+          <t>16,77; 24,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 20,33</t>
+          <t>13,8; 20,09</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 12,43</t>
+          <t>7,38; 10,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 10,43</t>
+          <t>6,4; 9,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,86</t>
+          <t>8,67; 12,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,42</t>
+          <t>7,45; 10,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 10,89</t>
+          <t>8,47; 11,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,75</t>
+          <t>7,19; 9,73</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -1025,22 +1025,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3581</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>8738</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2671</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4832; 14317</t>
+          <t>1974; 10706</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>559; 6573</t>
+          <t>1338; 7553</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2071; 10067</t>
+          <t>4519; 15036</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1376; 8435</t>
+          <t>747; 6484</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8232; 21101</t>
+          <t>8372; 20834</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2981; 11561</t>
+          <t>2963; 11681</t>
         </is>
       </c>
     </row>
@@ -1143,22 +1143,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28417</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24606</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>30289</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>28133</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28417</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22437; 39597</t>
+          <t>21487; 38294</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20410; 37435</t>
+          <t>17190; 34237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20439; 37101</t>
+          <t>22505; 38794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17741; 33945</t>
+          <t>20987; 37633</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47644; 71004</t>
+          <t>48453; 71873</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41972; 65844</t>
+          <t>42567; 65571</t>
         </is>
       </c>
     </row>
@@ -1261,22 +1261,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>33863</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29430</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>34102</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>31492</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>33863</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25805; 43757</t>
+          <t>25502; 42984</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23612; 40121</t>
+          <t>22063; 37660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25957; 43338</t>
+          <t>26233; 43452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21624; 37211</t>
+          <t>24815; 40723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>56569; 80845</t>
+          <t>56337; 81513</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49716; 73027</t>
+          <t>49566; 72147</t>
         </is>
       </c>
     </row>
@@ -1379,22 +1379,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>73130</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>62296</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>67235</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61583; 87539</t>
+          <t>55239; 80215</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50423; 73028</t>
+          <t>47226; 70514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55595; 81302</t>
+          <t>61013; 86633</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46929; 69529</t>
+          <t>52170; 76515</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122203; 158271</t>
+          <t>123103; 161549</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>104562; 140196</t>
+          <t>103401; 139952</t>
         </is>
       </c>
     </row>
